--- a/zawodnicy_us.xlsx
+++ b/zawodnicy_us.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C189"/>
+  <dimension ref="A1:C181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,7 @@
           <t>Jordan</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>[Niemcy] SpVgg Greuther Fürth</t>
@@ -618,364 +619,364 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ventura</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Amon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[Meksyk] CD Irapuato</t>
+          <t>[Austria] SKN St. Pölten</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Markus</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amon</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[Austria] SKN St. Pölten</t>
+          <t>[Dania] Lyngby Boldklub</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Markus</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Arce</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[Dania] Lyngby Boldklub</t>
+          <t>[Meksyk] Deportivo Toluca</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arce</t>
+          <t>Arfsten</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[Meksyk] Deportivo Toluca</t>
+          <t>[Anglia] FC Middlesbrough</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Femi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arfsten</t>
+          <t>Awodesu</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[Anglia] FC Middlesbrough</t>
+          <t>[Szwecja] Helsingborg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Femi</t>
+          <t>Folarin</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Awodesu</t>
+          <t>Balogun</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[Szwecja] Helsingborg</t>
+          <t>[Monako] AS Monaco</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Folarin</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Balogun</t>
+          <t>Barrios Cristales</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[Monako] AS Monaco</t>
+          <t>[Nowa Zelandia] Auckland United FC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Barrios Cristales</t>
+          <t>Beavers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Auckland United FC</t>
+          <t>[Dania] Bröndby IF</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Beavers</t>
+          <t>Beer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[Dania] Bröndby IF</t>
+          <t>[Nowa Zelandia] Auckland United FC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Beer</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Auckland United FC</t>
+          <t>[Austria] LASK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bello</t>
+          <t>Berhalter</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[Austria] LASK</t>
+          <t>[Anglia] FC Middlesbrough</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Berhalter</t>
+          <t>Bombino</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[Anglia] FC Middlesbrough</t>
+          <t>[Anglia] Stoke City</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bombino</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[Anglia] Stoke City</t>
+          <t>[Nowa Zelandia] Island Bay United</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Borella</t>
+          <t>Borso</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Island Bay United</t>
+          <t>[Szkocja] Greenock Morton FC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Terrence</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Borso</t>
+          <t>Boyd</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[Szkocja] Greenock Morton FC</t>
+          <t>[Niemcy] SV Waldhof Mannheim</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Terrence</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Boyd</t>
+          <t>Braman</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[Niemcy] SV Waldhof Mannheim</t>
+          <t>[Filipiny] Maharlika FC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Shaft</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Braman</t>
+          <t>Brewer Jr.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[Filipiny] Maharlika FC</t>
+          <t>[Malta] Birkirkara FC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shaft</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brewer Jr.</t>
+          <t>Burney</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[Malta] Birkirkara FC</t>
+          <t>[Irlandia] Drogheda United FC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Gianluca</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Burney</t>
+          <t>Busio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[Irlandia] Drogheda United FC</t>
+          <t>[Włochy] Venezia FC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gianluca</t>
+          <t>Quincy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Busio</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[Włochy] Venezia FC</t>
+          <t>[Austria] WSG Tirol</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Quincy</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[Austria] WSG Tirol</t>
+          <t>[Niemcy] SV 07 Elversberg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -985,82 +986,82 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[Niemcy] SV 07 Elversberg</t>
+          <t>[Anglia] West Bromwich Albion</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Johnny</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Campbell</t>
+          <t>Cardoso</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[Anglia] West Bromwich Albion</t>
+          <t>[Hiszpania] Atlético Madryt</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Johnny</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cardoso</t>
+          <t>Carleton</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[Hiszpania] Atlético Madryt</t>
+          <t>[Szwecja] Sandvikens IF</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Carleton</t>
+          <t>Carr</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[Szwecja] Sandvikens IF</t>
+          <t>[Nowa Zelandia] Western Suburbs FC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Carr</t>
+          <t>Carrera</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Western Suburbs FC</t>
+          <t>[Meksyk] Tigres UANL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Nico</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1070,2555 +1071,2419 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[Meksyk] Tigres UANL</t>
+          <t>[Meksyk] CF Atlante</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nico</t>
+          <t>Cameron</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Carrera</t>
+          <t>Carter-Vickers</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[Meksyk] CF Atlante</t>
+          <t>[Szkocja] Celtic Glasgow</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cameron</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Carter-Vickers</t>
+          <t>Castañeda</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[Szkocja] Celtic Glasgow</t>
+          <t>[Niemcy] SC Paderborn 07</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Castañeda</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[Niemcy] SC Paderborn 07</t>
+          <t>[Chinese Taipei] Taichung Futuro</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Edwin</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Castellanos</t>
+          <t>Cerrillo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[Meksyk] CD Irapuato</t>
+          <t>[Meksyk] CF América</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Chandler</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[Chinese Taipei] Taichung Futuro</t>
+          <t>[Niemcy] Eintracht Frankfurt</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Edwin</t>
+          <t>Muhammed</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cerrillo</t>
+          <t>Colakovic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[Meksyk] CF América</t>
+          <t>[Bośnia i Hercegowina] NK Travnik</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Jaidyn</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Contreras</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[Niemcy] Eintracht Frankfurt</t>
+          <t>[Meksyk] Tigres UANL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Muhammed</t>
+          <t>Mael</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Colakovic</t>
+          <t>Corboz</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>[Bośnia i Hercegowina] NK Travnik</t>
+          <t>[Francja] Grenoble Foot 38</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jaidyn</t>
+          <t>Benja</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Contreras</t>
+          <t>Cremaschi</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[Meksyk] Tigres UANL</t>
+          <t>[Włochy] Parma Calcio 1913</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mael</t>
+          <t>Mauricio</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Corboz</t>
+          <t>Cuevas</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[Francja] Grenoble Foot 38</t>
+          <t>[Meksyk] Santos Laguna</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alfredo</t>
+          <t>Christopher</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cortez</t>
+          <t>Cupps</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[Filipiny] One Taguig FC</t>
+          <t>[Szkocja] Greenock Morton FC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Benja</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cremaschi</t>
+          <t>De Corte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[Włochy] Parma Calcio 1913</t>
+          <t>[Holandia] FC Den Bosch</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mauricio</t>
+          <t>Giorgio</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cuevas</t>
+          <t>De Marzi</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[Meksyk] Santos Laguna</t>
+          <t>[Włochy] AS Roma</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Christopher</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cupps</t>
+          <t>Dennison</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[Szkocja] Greenock Morton FC</t>
+          <t>[Irlandia] Drogheda United FC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Sergiño</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Dest</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[Hiszpania] CE Sabadell B</t>
+          <t>[Holandia] PSV Eindhoven</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Grayson</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>De Corte</t>
+          <t>Dettoni</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[Holandia] FC Den Bosch</t>
+          <t>[Niemcy] SV Darmstadt 98</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Giorgio</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>De Marzi</t>
+          <t>Deziel Jr.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[Włochy] AS Roma</t>
+          <t>[Polska] Legia Warszawa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Maximilian</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dennison</t>
+          <t>Dietz</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[Irlandia] Drogheda United FC</t>
+          <t>[Polska] Górnik Zabrze</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sergiño</t>
+          <t>Taner</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dest</t>
+          <t>Dogan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[Holandia] PSV Eindhoven</t>
+          <t>[Walia] Holywell Town</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Grayson</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dettoni</t>
+          <t>Douglas</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>[Niemcy] SV Darmstadt 98</t>
+          <t>[Tajlandia] Chainat Hornbill FC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deziel Jr.</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>[Polska] Legia Warszawa</t>
+          <t>[Nowa Zelandia] Wellington Phoenix</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Maximilian</t>
+          <t>Emiliano</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dietz</t>
+          <t>Duran</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[Polska] Górnik Zabrze</t>
+          <t>[Nowa Zelandia] Waterside Karori AFC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Taner</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dogan</t>
+          <t>Duru</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[Walia] Holywell Town</t>
+          <t>[Anglia] Carlisle United</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Benny</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[Tajlandia] Chainat Hornbill FC</t>
+          <t>[Meksyk] FC Juárez</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Josué</t>
+          <t>Tristin</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dubón</t>
+          <t>Evans</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[Salwador] Nacional FC</t>
+          <t>[Estonia] FC Nomme United</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Falco</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Wellington Phoenix</t>
+          <t>[Nowa Zelandia] Ferrymead Bays FC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Emiliano</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Duran</t>
+          <t>Farfán</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Waterside Karori AFC</t>
+          <t>[Meksyk] Tigres UANL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Duru</t>
+          <t>Flach</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[Anglia] Carlisle United</t>
+          <t>[Niemcy] VfL Osnabrück</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Benny</t>
+          <t>CJ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Fodrey</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[Meksyk] FC Juárez</t>
+          <t>[Szkocja] Falkirk FC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Tristin</t>
+          <t>Marlon</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Evans</t>
+          <t>Fossey</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[Estonia] FC Nomme United</t>
+          <t>[Belgia] Standard Liège</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Falco</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Ferrymead Bays FC</t>
+          <t>[Hiszpania] Villarreal CF</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>José</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Farfán</t>
+          <t>Gallegos</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[Meksyk] Tigres UANL</t>
+          <t>[Bułgaria] Botev Vratsa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Flach</t>
+          <t>Gioacchini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[Niemcy] VfL Osnabrück</t>
+          <t>[Hiszpania] CE Sabadell FC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CJ</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fodrey</t>
+          <t>Gooch</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[Szkocja] Falkirk FC</t>
+          <t>[Anglia] Huddersfield Town</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Marlon</t>
+          <t>Zavier</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fossey</t>
+          <t>Gozo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[Belgia] Standard Liège</t>
+          <t>[Anglia] Crystal Palace</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Grimm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[Hiszpania] Villarreal CF</t>
+          <t>[Andora] Club Esportiu Carroi</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gallegos</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[Bułgaria] Botev Vratsa</t>
+          <t>[Niemcy] VfL Osnabrück</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Griffin</t>
+          <t>Tigran</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Garnett</t>
+          <t>Hakobyan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[Węgry] Ferencvárosi TC II</t>
+          <t>[Armenia] FC Ararat Erewan II</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gioacchini</t>
+          <t>Harangi</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[Hiszpania] CE Sabadell FC</t>
+          <t>[Węgry] Zalaegerszeg</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gooch</t>
+          <t>Hartmann</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>[Anglia] Huddersfield Town</t>
+          <t>[Szwecja] Östers IF</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Zavier</t>
+          <t>Alonso</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gozo</t>
+          <t>Hernández</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>[Anglia] Crystal Palace</t>
+          <t>[Kostaryka] CS Cartaginés</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Grimm</t>
+          <t>Hickey</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>[Andora] Club Esportiu Carroi</t>
+          <t>[Irlandia] Bohemian Football Club</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Gómez</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[Niemcy] VfL Osnabrück</t>
+          <t>[Szwajcaria] Grasshopper Club Zurych</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tigran</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hakobyan</t>
+          <t>Hoard</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[Armenia] FC Ararat Erewan II</t>
+          <t>[Serbia] OFK Belgrad</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Harangi</t>
+          <t>Hoffmann</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[Węgry] Zalaegerszeg</t>
+          <t>[Szwecja] Mjällby AIF</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hartmann</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>[Szwecja] Östers IF</t>
+          <t>[Dania] Sønderjyske</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Alonso</t>
+          <t>Eduvie</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hernández</t>
+          <t>Ikoba</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>[Kostaryka] CS Cartaginés</t>
+          <t>[Serbia] FK Zemun</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hickey</t>
+          <t>Innes</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[Irlandia] Bohemian Football Club</t>
+          <t>[Nowa Zelandia] Tauranga City AFC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Alexis</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Iturria</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>[Szwajcaria] Grasshopper Club Zurych</t>
+          <t>[Urugwaj] Paysandú FC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Andres</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Hoard</t>
+          <t>Jasson</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>[Serbia] OFK Belgrad</t>
+          <t>[Dania] AaB</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Bryang</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Hoffmann</t>
+          <t>Kayo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>[Szwecja] Mjällby AIF</t>
+          <t>[Belgia] OH Leuven</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>Kelman</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>[Dania] Sønderjyske</t>
+          <t>[Anglia] Charlton Athletic</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Eduvie</t>
+          <t>Preston</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ikoba</t>
+          <t>Kilwien</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>[Serbia] FK Zemun</t>
+          <t>[Kostaryka] Escorpiones de Belén</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Colin</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Innes</t>
+          <t>Klinsmann</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Tauranga City AFC</t>
+          <t>[Włochy] Cesena FC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Alexis</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Iturria</t>
+          <t>Kochen</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>[Urugwaj] Paysandú FC</t>
+          <t>[Dania] Lyngby Boldklub</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Andres</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jasson</t>
+          <t>Kócs-Washburn</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>[Dania] AaB</t>
+          <t>[Węgry] Tiszakécskei LC</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Stiven</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jimenez</t>
+          <t>Lambe</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>[Brazylia] Fluminense FC U20</t>
+          <t>[Irlandia] Drogheda United FC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Bryang</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kayo</t>
+          <t>Landreth</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>[Belgia] OH Leuven</t>
+          <t>[Brunei Darussalam] Kasuka FC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kelman</t>
+          <t>Lansing</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>[Anglia] Charlton Athletic</t>
+          <t>[Norwegia] Kristiansund BK</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Preston</t>
+          <t>Morais</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kilwien</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>[Kostaryka] Escorpiones de Belén</t>
+          <t>[Gibraltar] FC Hound Dogs</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Danny</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Klinsmann</t>
+          <t>Leyva</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>[Włochy] Cesena FC</t>
+          <t>[Meksyk] Club Necaxa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Aidan</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kochen</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>[Dania] Lyngby Boldklub</t>
+          <t>[Dania] Akademisk Boldklub</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kócs-Washburn</t>
+          <t>Luglio</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>[Węgry] Tiszakécskei LC</t>
+          <t>[Gibraltar] FC Hound Dogs</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Kristoffer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lambe</t>
+          <t>Lund</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>[Irlandia] Drogheda United FC</t>
+          <t>[Anglia] Birmingham City</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Landreth</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>[Brunei Darussalam] Kasuka FC</t>
+          <t>[Wietnam] Hong Linh Ha Tinh FC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lansing</t>
+          <t>Malone</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>[Norwegia] Kristiansund BK</t>
+          <t>[Niemcy] FC Energie Cottbus</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Morais</t>
+          <t>Lennard</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Maloney</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>[Gibraltar] FC Hound Dogs</t>
+          <t>[Niemcy] 1.FSV Mainz 05</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Hector</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Leyva</t>
+          <t>Marin</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>[Meksyk] Club Necaxa</t>
+          <t>[Nowa Zelandia] Wanaka FC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Aidan</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>McCue</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>[Dania] Akademisk Boldklub</t>
+          <t>[Szwecja] Örebro SK</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Luglio</t>
+          <t>McGlynn</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>[Gibraltar] FC Hound Dogs</t>
+          <t>[Anglia] Stoke City</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Kristoffer</t>
+          <t>Weston</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lund</t>
+          <t>McKennie</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>[Anglia] Birmingham City</t>
+          <t>[Włochy] Juventus Turyn</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>McKenzie</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>[Wietnam] Hong Linh Ha Tinh FC</t>
+          <t>[Francja] FC Toulouse</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Malone</t>
+          <t>McLagan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>[Niemcy] FC Energie Cottbus</t>
+          <t>[Islandia] Fram Reykjavík</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Lennard</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Maloney</t>
+          <t>McWoods</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>[Niemcy] 1.FSV Mainz 05</t>
+          <t>[Irlandia Północna] Cliftonville FC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Cruz</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mansaray</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>[Wietnam] Thai Nguyen FC</t>
+          <t>[Meksyk] CD Tapatío</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Hector</t>
+          <t>Benji</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Marin</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Wanaka FC</t>
+          <t>[Korea Południowa] Ulsan HD FC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Matko</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>McCue</t>
+          <t>Miljevic</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>[Szwecja] Örebro SK</t>
+          <t>[Argentyna] Racing Club</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>McGlynn</t>
+          <t>Montesinos</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>[Anglia] Stoke City</t>
+          <t>[Hong Kong] Hong Kong Football Club</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Weston</t>
+          <t>Jiovanny</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>McKennie</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>[Włochy] Juventus Turyn</t>
+          <t>[Nowa Zelandia] Wellington Phoenix FC Reserves</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Aidan</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>McKenzie</t>
+          <t>Morris</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>[Francja] FC Toulouse</t>
+          <t>[Anglia] FC Middlesbrough</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>McLagan</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>[Islandia] Fram Reykjavík</t>
+          <t>[Austria] WSG Tirol</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>McWoods</t>
+          <t>Murrell</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>[Irlandia Północna] Cliftonville FC</t>
+          <t>[Szkocja] Falkirk FC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cruz</t>
+          <t>Yunus</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Musah</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>[Meksyk] CD Tapatío</t>
+          <t>[Włochy] AC Milan</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Benji</t>
+          <t>Trevin</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Myers</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>[Korea Południowa] Ulsan HD FC</t>
+          <t>[Nowa Zelandia] Nelson Suburbs FC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Matko</t>
+          <t>Andrija</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Miljevic</t>
+          <t>Novakovich</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>[Argentyna] Racing Club</t>
+          <t>[Izrael] Maccabi Haifa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Zane</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Montesinos</t>
+          <t>Okoro</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>[Hong Kong] Hong Kong Football Club</t>
+          <t>[Anglia] Tranmere Rovers</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Jiovanny</t>
+          <t>Korede</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Osundina</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Wellington Phoenix FC Reserves</t>
+          <t>[Turcja] Muglaspor</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Aidan</t>
+          <t>Evan</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Morris</t>
+          <t>Paez</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>[Anglia] FC Middlesbrough</t>
+          <t>[Nowa Zelandia] Birkenhead United</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Palmer-Brown</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>[Austria] WSG Tirol</t>
+          <t>[Grecja] Panathinaikos</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Murrell</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>[Szkocja] Falkirk FC</t>
+          <t>[Holandia] FC Utrecht</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Yunus</t>
+          <t>Ricardo</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Musah</t>
+          <t>Pepi</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>[Włochy] AC Milan</t>
+          <t>[Holandia] PSV Eindhoven</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Trevin</t>
+          <t>Nebiyou</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Myers</t>
+          <t>Perry</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Nelson Suburbs FC</t>
+          <t>[Dania] Kolding IF</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Andrija</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Novakovich</t>
+          <t>Phipps</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>[Izrael] Maccabi Haifa</t>
+          <t>[Nowa Zelandia] Auckland United FC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Zane</t>
+          <t>Kayden</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Okoro</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>[Anglia] Tranmere Rovers</t>
+          <t>[Belgia] Jong Genk</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Korede</t>
+          <t>Donovan</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Osundina</t>
+          <t>Pines</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>[Turcja] Muglaspor</t>
+          <t>[Austria] Grazer AK 1902</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Evan</t>
+          <t>Walter</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Paez</t>
+          <t>Portales</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Birkenhead United</t>
+          <t>[Meksyk] CF Atlante</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Rokas</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Palmer-Brown</t>
+          <t>Pukstas</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>[Grecja] Panathinaikos</t>
+          <t>[Anglia] FC Middlesbrough</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Pulisic</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>[Holandia] FC Utrecht</t>
+          <t>[Włochy] AC Milan</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Ricardo</t>
+          <t>Shadi</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Pepi</t>
+          <t>Ramzi Bouri</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>[Holandia] PSV Eindhoven</t>
+          <t>[Katar] Muaither SC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Nebiyou</t>
+          <t>Jacobo</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Perry</t>
+          <t>Reyes</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>[Dania] Kolding IF</t>
+          <t>[Meksyk] Venados FC Yucatán</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Giovanni</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Phipps</t>
+          <t>Reyna</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Auckland United FC</t>
+          <t>[Francja] RC Strasbourg Alsace</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kayden</t>
+          <t>Bryan</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Reynolds</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>[Belgia] Jong Genk</t>
+          <t>[Francja] Rennes</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Donovan</t>
+          <t>Johnny</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Pines</t>
+          <t>Reynolds</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>[Austria] Grazer AK 1902</t>
+          <t>[Nowa Zelandia] Nelson Suburbs FC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Walter</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Portales</t>
+          <t>Richards</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>[Meksyk] CF Atlante</t>
+          <t>[Anglia] Crystal Palace</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Rokas</t>
+          <t>Caden</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pukstas</t>
+          <t>Robert McLagan</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>[Anglia] FC Middlesbrough</t>
+          <t>[Islandia] ÍF Grótta</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Antonee</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Pulisic</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>[Włochy] AC Milan</t>
+          <t>[Anglia] FC Fulham</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Shadi</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ramzi Bouri</t>
+          <t>Rodriguez</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>[Katar] Muaither SC</t>
+          <t>[Nowa Zelandia] Birkenhead United</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Jacobo</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Reyes</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>[Meksyk] Venados FC Yucatán</t>
+          <t>[Meksyk] Atlético de San Luis</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Giovanni</t>
+          <t>Bryan</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Reyna</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>[Francja] RC Strasbourg Alsace</t>
+          <t>[Meksyk] FC Juárez</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>Evan</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Rotundo</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>[Francja] Rennes</t>
+          <t>[Czechy] Dukla Praha</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Johnny</t>
+          <t>Fady</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Said Omar</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Nelson Suburbs FC</t>
+          <t>[Andora] Club Esportiu Carroi</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Kenny</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Richards</t>
+          <t>Saief</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>[Anglia] Crystal Palace</t>
+          <t>[Izrael] Maccabi Haifa</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Caden</t>
+          <t>Jesus</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Robert McLagan</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>[Islandia] ÍF Grótta</t>
+          <t>[Brunei Darussalam] Kasuka FC</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Antonee</t>
+          <t>Joe</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Scally</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>[Anglia] FC Fulham</t>
+          <t>[Niemcy] Borussia Mönchengladbach</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Rodriguez</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Birkenhead United</t>
+          <t>[Włochy] US Lecce</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Clancey</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Skea</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>[Meksyk] Atlético de San Luis</t>
+          <t>[Nowa Zelandia] Nelson Suburbs FC</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Skoczylas</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>[Meksyk] FC Juárez</t>
+          <t>[Islandia] KF Aegir</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Evan</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Rotundo</t>
+          <t>Slingsby</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>[Czechy] Dukla Praha</t>
+          <t>[Nowa Zelandia] Birkenhead United</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Fady</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Said Omar</t>
+          <t>Slonina</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>[Andora] Club Esportiu Carroi</t>
+          <t>[Anglia] Chelsea FC</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Kenny</t>
+          <t>Travian</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Saief</t>
+          <t>Sousa</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>[Izrael] Maccabi Haifa</t>
+          <t>[Dania] Akademisk Boldklub</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Jesus</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Soñora</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>[Brunei Darussalam] Kasuka FC</t>
+          <t>[Argentyna] CA Newell's Old Boys</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>Ellis</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Scally</t>
+          <t>Spikner</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>[Niemcy] Borussia Mönchengladbach</t>
+          <t>[Izrael] Maccabi Kiryat Gat</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Swenson</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>[Włochy] US Lecce</t>
+          <t>[Nowa Zelandia] Waterside Karori AFC</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Clancey</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Skea</t>
+          <t>Tessmann</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Nelson Suburbs FC</t>
+          <t>[Francja] Olympique Lyon</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Malik</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Skoczylas</t>
+          <t>Tillman</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>[Islandia] KF Aegir</t>
+          <t>[Niemcy] Bayer 04 Leverkusen</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Devin</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Slingsby</t>
+          <t>Tolkin</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Birkenhead United</t>
+          <t>[Niemcy] Holstein Kiel</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Slonina</t>
+          <t>Tomkinson</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>[Anglia] Chelsea FC</t>
+          <t>[Anglia] Cheltenham Town</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Travian</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Sousa</t>
+          <t>Toye</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>[Dania] Akademisk Boldklub</t>
+          <t>[Niemcy] FC Ingolstadt 04</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Auston</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Soñora</t>
+          <t>Trusty</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>[Argentyna] CA Newell's Old Boys</t>
+          <t>[Szkocja] Celtic Glasgow</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ellis</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Spikner</t>
+          <t>Velasquez</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>[Izrael] Maccabi Kiryat Gat</t>
+          <t>[Czechy] Dukla Praha</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Swenson</t>
+          <t>Walters</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Waterside Karori AFC</t>
+          <t>[Irlandia] Bohemian Football Club</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Tessmann</t>
+          <t>Weah</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>[Francja] Olympique Lyon</t>
+          <t>[Francja] Olympique Marseille</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Malik</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Tillman</t>
+          <t>Wesseh</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>[Niemcy] Bayer 04 Leverkusen</t>
+          <t>[Norwegia] Fredrikstad FK</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tolkin</t>
+          <t>Wigg</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>[Niemcy] Holstein Kiel</t>
+          <t>[Nowa Zelandia] Western Suburbs FC</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Caleb</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tomkinson</t>
+          <t>Wiley</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>[Anglia] Cheltenham Town</t>
+          <t>[Anglia] Preston North End</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>JJ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Toye</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>[Niemcy] FC Ingolstadt 04</t>
+          <t>[Szkocja] Heart of Midlothian FC</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Auston</t>
+          <t>Haji</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Trusty</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>[Szkocja] Celtic Glasgow</t>
+          <t>[Anglia] Coventry City</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Isaiah</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Velasquez</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>[Czechy] Dukla Praha</t>
+          <t>[Niemcy] Arminia Bielefeld</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kahveh</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Walters</t>
+          <t>Zahiroleslam</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>[Irlandia] Bohemian Football Club</t>
+          <t>[Polska] Cracovia</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Álex</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Weah</t>
+          <t>Zendejas</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>[Francja] Olympique Marseille</t>
+          <t>[Meksyk] CF América</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Wesseh</t>
+          <t>de Vries</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>[Norwegia] Fredrikstad FK</t>
+          <t>[Holandia] FC Den Bosch</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Konrad</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Wigg</t>
+          <t>de la Fuente</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
-        <is>
-          <t>[Nowa Zelandia] Western Suburbs FC</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Caleb</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Wiley</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>[Anglia] Preston North End</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>JJ</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>[Szkocja] Heart of Midlothian FC</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Haji</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Wright</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>[Anglia] Coventry City</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Isaiah</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Young</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>[Niemcy] Arminia Bielefeld</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Kahveh</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Zahiroleslam</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>[Polska] Cracovia</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Álex</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Zendejas</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>[Meksyk] CF América</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>de Vries</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>[Holandia] FC Den Bosch</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Konrad</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>de la Fuente</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
         <is>
           <t>[Hiszpania] Sporting Gijón</t>
         </is>

--- a/zawodnicy_us.xlsx
+++ b/zawodnicy_us.xlsx
@@ -439,7 +439,6 @@
           <t>Jordan</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>[Niemcy] SpVgg Greuther Fürth</t>
@@ -1003,7 +1002,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[Hiszpania] Atlético Madryt</t>
+          <t>[Hiszpania] Atlético Madrid</t>
         </is>
       </c>
     </row>
